--- a/data/trans_orig/DC-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/DC-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2007</t>
+          <t>Población con dolor crónico en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>257500</t>
+          <t>257286</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>314015</t>
+          <t>317677</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>425231</t>
+          <t>418478</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>488699</t>
+          <t>490055</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>696715</t>
+          <t>699059</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>785187</t>
+          <t>784546</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>717708</t>
+          <t>714046</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>774223</t>
+          <t>774437</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>826414</t>
+          <t>825058</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>889882</t>
+          <t>896635</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1561648</t>
+          <t>1562289</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1650120</t>
+          <t>1647776</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,21%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>192607</t>
+          <t>192403</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>247184</t>
+          <t>248110</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>348670</t>
+          <t>348064</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>415746</t>
+          <t>414692</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>558542</t>
+          <t>558702</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>646935</t>
+          <t>645191</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1446229</t>
+          <t>1445303</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1500806</t>
+          <t>1501010</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1171927</t>
+          <t>1172981</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1239003</t>
+          <t>1239609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2634151</t>
+          <t>2635895</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2722544</t>
+          <t>2722384</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,97%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54540</t>
+          <t>53668</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87059</t>
+          <t>87307</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86641</t>
+          <t>88550</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123339</t>
+          <t>125630</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>151113</t>
+          <t>150932</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>200872</t>
+          <t>200256</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>464349</t>
+          <t>464101</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>496868</t>
+          <t>497740</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>353073</t>
+          <t>350782</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>389771</t>
+          <t>387862</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>826948</t>
+          <t>827564</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>876707</t>
+          <t>876888</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,32%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>534641</t>
+          <t>532336</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>619071</t>
+          <t>618642</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>893553</t>
+          <t>887963</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>999137</t>
+          <t>995197</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1444561</t>
+          <t>1447744</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1583231</t>
+          <t>1578929</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2657472</t>
+          <t>2657901</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2741902</t>
+          <t>2744207</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2380060</t>
+          <t>2384000</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2485644</t>
+          <t>2491234</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5072510</t>
+          <t>5076812</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5211180</t>
+          <t>5207997</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2012</t>
+          <t>Población con dolor crónico en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>146670</t>
+          <t>148514</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>197673</t>
+          <t>197125</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>382044</t>
+          <t>384061</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>452015</t>
+          <t>453143</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>540649</t>
+          <t>548299</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>628097</t>
+          <t>632773</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>776970</t>
+          <t>777518</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>827973</t>
+          <t>826129</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>885782</t>
+          <t>884654</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>955753</t>
+          <t>953736</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1684343</t>
+          <t>1679667</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1771791</t>
+          <t>1764141</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>131575</t>
+          <t>138072</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>183309</t>
+          <t>185520</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>310091</t>
+          <t>312390</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>379930</t>
+          <t>380702</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>463119</t>
+          <t>463501</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>549034</t>
+          <t>549365</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1780648</t>
+          <t>1778437</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1832382</t>
+          <t>1825885</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1377873</t>
+          <t>1377101</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1447712</t>
+          <t>1445413</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3172726</t>
+          <t>3172395</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3258641</t>
+          <t>3258259</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36499</t>
+          <t>37951</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68385</t>
+          <t>72325</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104404</t>
+          <t>105220</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92170</t>
+          <t>92307</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133880</t>
+          <t>134018</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>444682</t>
+          <t>443230</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>354227</t>
+          <t>353411</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>390246</t>
+          <t>386306</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>805933</t>
+          <t>805795</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>847643</t>
+          <t>847506</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>320740</t>
+          <t>319646</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>395538</t>
+          <t>393850</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>801468</t>
+          <t>798461</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>902297</t>
+          <t>903238</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1140098</t>
+          <t>1139765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1274730</t>
+          <t>1265201</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3024244</t>
+          <t>3025932</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3099042</t>
+          <t>3100136</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2651933</t>
+          <t>2650992</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2752762</t>
+          <t>2755769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5699282</t>
+          <t>5708811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5833914</t>
+          <t>5834247</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2016</t>
+          <t>Población con dolor crónico en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97730</t>
+          <t>98608</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>137296</t>
+          <t>136332</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>231475</t>
+          <t>234410</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>289816</t>
+          <t>291952</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>346745</t>
+          <t>340413</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>417160</t>
+          <t>416171</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>617051</t>
+          <t>618015</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>656617</t>
+          <t>655739</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>704844</t>
+          <t>702708</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>763185</t>
+          <t>760250</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1331847</t>
+          <t>1332836</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1402262</t>
+          <t>1408594</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,54%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>134901</t>
+          <t>136800</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>185507</t>
+          <t>185333</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>281915</t>
+          <t>283090</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>347299</t>
+          <t>351006</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>433123</t>
+          <t>433248</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>519156</t>
+          <t>517156</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1890878</t>
+          <t>1891052</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1941484</t>
+          <t>1939585</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1641001</t>
+          <t>1637294</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1706385</t>
+          <t>1705210</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3545529</t>
+          <t>3547529</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3631562</t>
+          <t>3631437</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32179</t>
+          <t>34093</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59631</t>
+          <t>62998</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57563</t>
+          <t>57882</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89499</t>
+          <t>91961</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98068</t>
+          <t>96867</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140885</t>
+          <t>139583</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>487255</t>
+          <t>483888</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>514707</t>
+          <t>512793</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>459641</t>
+          <t>457179</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>491577</t>
+          <t>491258</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>955142</t>
+          <t>956444</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>997959</t>
+          <t>999160</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>287371</t>
+          <t>286662</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>357037</t>
+          <t>354113</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>601748</t>
+          <t>606119</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>701767</t>
+          <t>700251</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>909588</t>
+          <t>916834</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1030247</t>
+          <t>1030627</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3020581</t>
+          <t>3023505</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3090247</t>
+          <t>3090956</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2830333</t>
+          <t>2831849</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2930352</t>
+          <t>2925981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5879471</t>
+          <t>5879091</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6000130</t>
+          <t>5992884</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,73%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2023</t>
+          <t>Población con dolor crónico en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>156840</t>
+          <t>158642</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>196375</t>
+          <t>196704</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>393696</t>
+          <t>392712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>437070</t>
+          <t>436027</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>562208</t>
+          <t>561766</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>620651</t>
+          <t>620374</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,83%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>318563</t>
+          <t>318234</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>358098</t>
+          <t>356296</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>318438</t>
+          <t>319481</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>361812</t>
+          <t>362796</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>649795</t>
+          <t>650072</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>708238</t>
+          <t>708680</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,78%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>297065</t>
+          <t>281903</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>476817</t>
+          <t>474851</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>758746</t>
+          <t>773480</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1265089</t>
+          <t>1317387</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1124135</t>
+          <t>1107557</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1861038</t>
+          <t>1794761</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1813510</t>
+          <t>1815476</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1993262</t>
+          <t>2008424</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>972734</t>
+          <t>920436</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1479077</t>
+          <t>1464343</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2667112</t>
+          <t>2733389</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3404015</t>
+          <t>3420593</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,54%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88175</t>
+          <t>88787</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125304</t>
+          <t>127297</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>199104</t>
+          <t>196914</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>241324</t>
+          <t>240061</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>295943</t>
+          <t>296000</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>356770</t>
+          <t>355942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>521319</t>
+          <t>519326</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>558448</t>
+          <t>557836</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>419139</t>
+          <t>420402</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>461359</t>
+          <t>463549</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>950316</t>
+          <t>951144</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1011143</t>
+          <t>1011086</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,35%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>538023</t>
+          <t>547752</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>767500</t>
+          <t>760552</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1410141</t>
+          <t>1409859</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1961415</t>
+          <t>1948328</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2012519</t>
+          <t>2012031</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2735244</t>
+          <t>2716898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2684389</t>
+          <t>2691337</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2913866</t>
+          <t>2904137</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1692379</t>
+          <t>1705466</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2243653</t>
+          <t>2243935</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4370439</t>
+          <t>4388785</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5093164</t>
+          <t>5093652</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/DC-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/DC-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>257286</t>
+          <t>256963</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>317677</t>
+          <t>312470</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>418478</t>
+          <t>419236</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>490055</t>
+          <t>488136</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>699059</t>
+          <t>694397</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>784546</t>
+          <t>784843</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>714046</t>
+          <t>719253</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>774437</t>
+          <t>774760</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>825058</t>
+          <t>826977</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>896635</t>
+          <t>895877</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1562289</t>
+          <t>1561992</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1647776</t>
+          <t>1652438</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,41%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>192403</t>
+          <t>194156</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>248110</t>
+          <t>250483</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>348064</t>
+          <t>351353</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>414692</t>
+          <t>413795</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>558702</t>
+          <t>556191</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>645191</t>
+          <t>643576</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1445303</t>
+          <t>1442930</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1501010</t>
+          <t>1499257</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1172981</t>
+          <t>1173878</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1239609</t>
+          <t>1236320</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2635895</t>
+          <t>2637510</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2722384</t>
+          <t>2724895</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53668</t>
+          <t>53532</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87307</t>
+          <t>85188</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88550</t>
+          <t>90243</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125630</t>
+          <t>126358</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150932</t>
+          <t>151425</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>200256</t>
+          <t>204707</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>464101</t>
+          <t>466220</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>497740</t>
+          <t>497876</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>350782</t>
+          <t>350054</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>387862</t>
+          <t>386169</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>827564</t>
+          <t>823113</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>876888</t>
+          <t>876395</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>532336</t>
+          <t>533223</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>618642</t>
+          <t>622922</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>887963</t>
+          <t>892353</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>995197</t>
+          <t>999527</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1447744</t>
+          <t>1439946</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1578929</t>
+          <t>1579800</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2657901</t>
+          <t>2653621</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2744207</t>
+          <t>2743320</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2384000</t>
+          <t>2379670</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2491234</t>
+          <t>2486844</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5076812</t>
+          <t>5075941</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5207997</t>
+          <t>5215795</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>148514</t>
+          <t>147276</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>197125</t>
+          <t>195840</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>384061</t>
+          <t>382609</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>453143</t>
+          <t>451647</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>548299</t>
+          <t>543204</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>632773</t>
+          <t>629194</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>777518</t>
+          <t>778803</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>826129</t>
+          <t>827367</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>884654</t>
+          <t>886150</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>953736</t>
+          <t>955188</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1679667</t>
+          <t>1683246</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1764141</t>
+          <t>1769236</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,51%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>138072</t>
+          <t>136100</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>185520</t>
+          <t>184459</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>312390</t>
+          <t>311470</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>380702</t>
+          <t>381340</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>463501</t>
+          <t>463447</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>549365</t>
+          <t>551381</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1778437</t>
+          <t>1779498</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1825885</t>
+          <t>1827857</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1377101</t>
+          <t>1376463</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1445413</t>
+          <t>1446333</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3172395</t>
+          <t>3170379</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3258259</t>
+          <t>3258313</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15856</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37951</t>
+          <t>36656</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72325</t>
+          <t>70667</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105220</t>
+          <t>106073</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92307</t>
+          <t>93949</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134018</t>
+          <t>135278</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>443230</t>
+          <t>444525</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>465325</t>
+          <t>465225</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>353411</t>
+          <t>352558</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>386306</t>
+          <t>387964</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>805795</t>
+          <t>804535</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>847506</t>
+          <t>845864</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,0%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>319646</t>
+          <t>321907</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>393850</t>
+          <t>392794</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>798461</t>
+          <t>797330</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>903238</t>
+          <t>897768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1139765</t>
+          <t>1133885</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1265201</t>
+          <t>1261755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3025932</t>
+          <t>3026988</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3100136</t>
+          <t>3097875</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2650992</t>
+          <t>2656462</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2755769</t>
+          <t>2756900</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5708811</t>
+          <t>5712257</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5834247</t>
+          <t>5840127</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,74%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98608</t>
+          <t>99498</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>136332</t>
+          <t>139589</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>234410</t>
+          <t>233713</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>291952</t>
+          <t>292686</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>340413</t>
+          <t>344995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>416171</t>
+          <t>415116</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>618015</t>
+          <t>614758</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>655739</t>
+          <t>654849</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>702708</t>
+          <t>701974</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>760250</t>
+          <t>760947</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1332836</t>
+          <t>1333891</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1408594</t>
+          <t>1404012</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,27%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>136800</t>
+          <t>137235</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>185333</t>
+          <t>187568</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>283090</t>
+          <t>284015</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>351006</t>
+          <t>351326</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>433248</t>
+          <t>433959</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>517156</t>
+          <t>516869</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1891052</t>
+          <t>1888817</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1939585</t>
+          <t>1939150</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1637294</t>
+          <t>1636974</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1705210</t>
+          <t>1704285</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3547529</t>
+          <t>3547816</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3631437</t>
+          <t>3630726</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,32%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34093</t>
+          <t>32976</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62998</t>
+          <t>59865</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57882</t>
+          <t>55706</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91961</t>
+          <t>89732</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96867</t>
+          <t>98108</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139583</t>
+          <t>141045</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>483888</t>
+          <t>487021</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>512793</t>
+          <t>513910</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>457179</t>
+          <t>459408</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>491258</t>
+          <t>493434</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>956444</t>
+          <t>954982</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>999160</t>
+          <t>997919</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>286662</t>
+          <t>290103</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>354113</t>
+          <t>359156</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>606119</t>
+          <t>602624</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>700251</t>
+          <t>700339</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>916834</t>
+          <t>910583</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1030627</t>
+          <t>1033178</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3023505</t>
+          <t>3018462</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3090956</t>
+          <t>3087515</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2831849</t>
+          <t>2831761</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2925981</t>
+          <t>2929476</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5879091</t>
+          <t>5876540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5992884</t>
+          <t>5999135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,82%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>176964</t>
+          <t>190294</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>158642</t>
+          <t>168765</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>196704</t>
+          <t>212348</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>415336</t>
+          <t>452606</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>392712</t>
+          <t>430711</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>436027</t>
+          <t>474493</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>592300</t>
+          <t>642900</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>561766</t>
+          <t>608789</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>620374</t>
+          <t>673340</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,08%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>337974</t>
+          <t>388235</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>318234</t>
+          <t>366181</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>356296</t>
+          <t>409764</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>340172</t>
+          <t>369432</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>319481</t>
+          <t>347545</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>362796</t>
+          <t>391327</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>678146</t>
+          <t>757667</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>650072</t>
+          <t>727227</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>708680</t>
+          <t>791778</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>56,53%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>411266</t>
+          <t>445924</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>281903</t>
+          <t>405383</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>474851</t>
+          <t>487194</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>934907</t>
+          <t>747582</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>773480</t>
+          <t>708307</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1317387</t>
+          <t>790733</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1346173</t>
+          <t>1193506</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1107557</t>
+          <t>1133299</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1794761</t>
+          <t>1251972</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1879061</t>
+          <t>1784642</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1815476</t>
+          <t>1743372</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2008424</t>
+          <t>1825183</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1302916</t>
+          <t>1423810</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>920436</t>
+          <t>1380659</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1464343</t>
+          <t>1463085</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3181977</t>
+          <t>3208453</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2733389</t>
+          <t>3149987</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3420593</t>
+          <t>3268660</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>106456</t>
+          <t>116920</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88787</t>
+          <t>97271</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127297</t>
+          <t>136812</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>220119</t>
+          <t>246618</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>196914</t>
+          <t>224945</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>240061</t>
+          <t>271492</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>326575</t>
+          <t>363538</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>296000</t>
+          <t>331760</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>355942</t>
+          <t>397448</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>540167</t>
+          <t>594667</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519326</t>
+          <t>574775</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>557836</t>
+          <t>614316</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>440344</t>
+          <t>488259</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>420402</t>
+          <t>463385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>463549</t>
+          <t>509932</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>980511</t>
+          <t>1082926</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>951144</t>
+          <t>1049016</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1011086</t>
+          <t>1114704</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,06%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>694687</t>
+          <t>753138</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>547752</t>
+          <t>701398</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>760552</t>
+          <t>804928</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1570362</t>
+          <t>1446807</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1409859</t>
+          <t>1394365</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1948328</t>
+          <t>1499459</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2265049</t>
+          <t>2199945</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2012031</t>
+          <t>2128314</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2716898</t>
+          <t>2279187</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2757202</t>
+          <t>2767545</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2691337</t>
+          <t>2715755</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2904137</t>
+          <t>2819285</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2083432</t>
+          <t>2281500</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1705466</t>
+          <t>2228848</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2243935</t>
+          <t>2333942</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4840634</t>
+          <t>5049045</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4388785</t>
+          <t>4969803</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5093652</t>
+          <t>5120676</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>70,64%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
